--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,14 +2258,14 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N14" t="n">
         <v>2.75</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.16</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>15</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.18</v>
+        <v>2.11</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.6</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,64 +2654,64 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.16</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>14</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,58 +2390,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.16</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.28</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,13 +2570,13 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="n">
         <v>1.6</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
         <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>18</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,16 +1778,16 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
         <v>1.6</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,64 +2258,64 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.16</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,14 +1466,14 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.85</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.16</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,64 +1994,64 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.75</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.14</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -172,12 +172,12 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Europe UEFA Champions League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -199,72 +199,72 @@
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
     <t>Vyškov</t>
   </si>
   <si>
-    <t>Hanácká</t>
+    <t>Qarabağ</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Skeid</t>
+    <t>Moss</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>FCSB</t>
+  </si>
+  <si>
     <t>Ludogorets</t>
   </si>
   <si>
-    <t>FCSB</t>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
   </si>
   <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -292,70 +292,70 @@
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
+    <t>Shelbourne</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
+    <t>Sogndal</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
     <t>Aalesund</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
+    <t>Shkendija</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Shkendija</t>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Artsakh</t>
+  </si>
+  <si>
+    <t>Rangers</t>
   </si>
   <si>
     <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Rangers</t>
   </si>
   <si>
     <t>Lech Poznań</t>
@@ -1218,10 +1218,10 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1245,13 +1245,13 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1263,58 +1263,58 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1450,10 +1450,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -1477,13 +1477,13 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1495,58 +1495,58 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1798,10 +1798,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
@@ -1914,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>67</v>
@@ -1941,13 +1941,13 @@
         <v>120</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1959,58 +1959,58 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,7 +2030,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -2057,13 +2057,13 @@
         <v>120</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2075,58 +2075,58 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="s">
         <v>121</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -2265,7 +2265,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2378,10 +2378,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
@@ -2494,7 +2494,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -2521,13 +2521,13 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2539,58 +2539,58 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2610,10 +2610,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -2637,13 +2637,13 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2655,58 +2655,58 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -2726,7 +2726,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
         <v>57</v>
@@ -2753,13 +2753,13 @@
         <v>120</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2771,58 +2771,58 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="s">
         <v>121</v>
@@ -2842,7 +2842,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -2869,76 +2869,76 @@
         <v>120</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="s">
         <v>121</v>
@@ -2985,13 +2985,13 @@
         <v>120</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="s">
         <v>121</v>
@@ -3074,7 +3074,7 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
         <v>56</v>
@@ -3101,76 +3101,76 @@
         <v>120</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="s">
         <v>121</v>
@@ -3190,7 +3190,7 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
         <v>56</v>
@@ -3217,76 +3217,76 @@
         <v>120</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ22" t="s">
         <v>121</v>
@@ -3309,7 +3309,7 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3422,7 +3422,7 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3538,7 +3538,7 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3657,7 +3657,7 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
@@ -3681,13 +3681,13 @@
         <v>120</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -3699,58 +3699,58 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="s">
         <v>121</v>
@@ -3770,7 +3770,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
         <v>56</v>
@@ -3797,13 +3797,13 @@
         <v>120</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
         <v>56</v>
@@ -3913,76 +3913,76 @@
         <v>120</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ28" t="s">
         <v>121</v>
@@ -4002,7 +4002,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
         <v>56</v>
@@ -4029,76 +4029,76 @@
         <v>120</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="s">
         <v>121</v>
@@ -4261,13 +4261,13 @@
         <v>120</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -4309,10 +4309,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4377,13 +4377,13 @@
         <v>120</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD32">
         <v>0</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -166,12 +166,12 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -184,69 +184,69 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025/2026</t>
   </si>
   <si>
-    <t>2025</t>
+    <t>New England II</t>
   </si>
   <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
     <t>Odd</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Skeid</t>
+    <t>Vyškov</t>
   </si>
   <si>
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Lyn</t>
+    <t>FK Bodo - Glimt</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>FCSB</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
@@ -283,63 +283,63 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
     <t>Stabæk</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Ranheim</t>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Opava</t>
   </si>
   <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Baník Ostrava II</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
+    <t>Strømsgodset</t>
   </si>
   <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
     <t>Shkendija</t>
   </si>
   <si>
@@ -349,10 +349,10 @@
     <t>Paphos</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Rangers</t>
   </si>
   <si>
     <t>Raufoss</t>
@@ -1102,10 +1102,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -1221,7 +1221,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1254,13 +1254,13 @@
         <v>2.55</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R5">
         <v>1.22</v>
@@ -1334,7 +1334,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1450,7 +1450,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -1477,13 +1477,13 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1495,58 +1495,58 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1566,7 +1566,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1798,7 +1798,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -1914,7 +1914,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
@@ -1941,13 +1941,13 @@
         <v>120</v>
       </c>
       <c r="L11">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1959,58 +1959,58 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,7 +2030,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -2057,13 +2057,13 @@
         <v>120</v>
       </c>
       <c r="L12">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2075,58 +2075,58 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>121</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -2262,7 +2262,7 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="M14">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="N14">
-        <v>18</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="P14">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Q14">
-        <v>4.8</v>
+        <v>2.33</v>
       </c>
       <c r="R14">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S14">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="U14">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="V14">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="W14">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Z14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AA14">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AB14">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD14">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE14">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="AH14">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="AI14">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2378,7 +2378,7 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2494,7 +2494,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -2521,13 +2521,13 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2539,58 +2539,58 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2610,7 +2610,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>57</v>
@@ -2637,76 +2637,76 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="M17">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S17">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T17">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="U17">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="V17">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Z17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA17">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AB17">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC17">
+        <v>2.75</v>
+      </c>
+      <c r="AD17">
         <v>2.25</v>
       </c>
-      <c r="AD17">
-        <v>2.38</v>
-      </c>
       <c r="AE17">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="AH17">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AI17">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -2726,7 +2726,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>57</v>
@@ -2753,13 +2753,13 @@
         <v>120</v>
       </c>
       <c r="L18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2771,58 +2771,58 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="s">
         <v>121</v>
@@ -2842,7 +2842,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -2869,76 +2869,76 @@
         <v>120</v>
       </c>
       <c r="L19">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH19">
-        <v>3.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI19">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AJ19" t="s">
         <v>121</v>
@@ -2958,7 +2958,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>57</v>
@@ -2985,76 +2985,76 @@
         <v>120</v>
       </c>
       <c r="L20">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH20">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="AI20">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AJ20" t="s">
         <v>121</v>
@@ -3077,7 +3077,7 @@
         <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -3193,7 +3193,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -3309,7 +3309,7 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3425,7 +3425,7 @@
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
+        <v>2.01</v>
+      </c>
+      <c r="M24">
+        <v>3.5</v>
+      </c>
+      <c r="N24">
+        <v>3.5</v>
+      </c>
+      <c r="O24">
+        <v>1.6</v>
+      </c>
+      <c r="P24">
+        <v>10</v>
+      </c>
+      <c r="Q24">
+        <v>2.55</v>
+      </c>
+      <c r="R24">
+        <v>1.34</v>
+      </c>
+      <c r="S24">
+        <v>2.95</v>
+      </c>
+      <c r="T24">
+        <v>2.55</v>
+      </c>
+      <c r="U24">
         <v>1.44</v>
       </c>
-      <c r="M24">
-        <v>4.5</v>
-      </c>
-      <c r="N24">
-        <v>6.5</v>
-      </c>
-      <c r="O24">
-        <v>1.33</v>
-      </c>
-      <c r="P24">
-        <v>13.5</v>
-      </c>
-      <c r="Q24">
-        <v>3.5</v>
-      </c>
-      <c r="R24">
-        <v>1.27</v>
-      </c>
-      <c r="S24">
-        <v>3.4</v>
-      </c>
-      <c r="T24">
-        <v>2.2</v>
-      </c>
-      <c r="U24">
-        <v>1.58</v>
-      </c>
       <c r="V24">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z24">
+        <v>1.2</v>
+      </c>
+      <c r="AA24">
+        <v>4</v>
+      </c>
+      <c r="AB24">
+        <v>1.67</v>
+      </c>
+      <c r="AC24">
+        <v>2.1</v>
+      </c>
+      <c r="AD24">
+        <v>2.88</v>
+      </c>
+      <c r="AE24">
+        <v>1.36</v>
+      </c>
+      <c r="AF24">
+        <v>1.73</v>
+      </c>
+      <c r="AG24">
+        <v>1.95</v>
+      </c>
+      <c r="AH24">
+        <v>5.5</v>
+      </c>
+      <c r="AI24">
         <v>1.11</v>
-      </c>
-      <c r="AA24">
-        <v>4.95</v>
-      </c>
-      <c r="AB24">
-        <v>1.61</v>
-      </c>
-      <c r="AC24">
-        <v>2.2</v>
-      </c>
-      <c r="AD24">
-        <v>2.33</v>
-      </c>
-      <c r="AE24">
-        <v>1.63</v>
-      </c>
-      <c r="AF24">
-        <v>1.82</v>
-      </c>
-      <c r="AG24">
-        <v>1.85</v>
-      </c>
-      <c r="AH24">
-        <v>3.72</v>
-      </c>
-      <c r="AI24">
-        <v>1.21</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3541,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
         <v>81</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M25">
+        <v>4.5</v>
+      </c>
+      <c r="N25">
+        <v>6.5</v>
+      </c>
+      <c r="O25">
+        <v>1.33</v>
+      </c>
+      <c r="P25">
+        <v>13.5</v>
+      </c>
+      <c r="Q25">
         <v>3.5</v>
       </c>
-      <c r="N25">
-        <v>3.5</v>
-      </c>
-      <c r="O25">
-        <v>1.6</v>
-      </c>
-      <c r="P25">
-        <v>10</v>
-      </c>
-      <c r="Q25">
-        <v>2.55</v>
-      </c>
       <c r="R25">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S25">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="V25">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="Z25">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AA25">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AE25">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH25">
-        <v>5.5</v>
+        <v>3.72</v>
       </c>
       <c r="AI25">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3657,7 +3657,7 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
@@ -3690,13 +3690,13 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R26">
         <v>1.22</v>
@@ -3773,7 +3773,7 @@
         <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -3889,7 +3889,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -4005,7 +4005,7 @@
         <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -4118,10 +4118,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
         <v>86</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -4261,76 +4261,76 @@
         <v>120</v>
       </c>
       <c r="L31">
+        <v>2.55</v>
+      </c>
+      <c r="M31">
+        <v>3.5</v>
+      </c>
+      <c r="N31">
+        <v>2.47</v>
+      </c>
+      <c r="O31">
+        <v>1.95</v>
+      </c>
+      <c r="P31">
+        <v>13.25</v>
+      </c>
+      <c r="Q31">
+        <v>1.91</v>
+      </c>
+      <c r="R31">
+        <v>1.31</v>
+      </c>
+      <c r="S31">
+        <v>3.1</v>
+      </c>
+      <c r="T31">
         <v>2.5</v>
       </c>
-      <c r="M31">
-        <v>3.55</v>
-      </c>
-      <c r="N31">
-        <v>2.39</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB31">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC31">
         <v>1.97</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="s">
         <v>121</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
         <v>88</v>
@@ -4377,76 +4377,76 @@
         <v>120</v>
       </c>
       <c r="L32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M32">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N32">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
         <v>1.85</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="s">
         <v>121</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -166,12 +166,12 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -184,84 +184,84 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025/2026</t>
+    <t>Sparta Praha II</t>
   </si>
   <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Odd</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
     <t>Skeid</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
     <t>FCSB</t>
   </si>
   <si>
-    <t>Ludogorets</t>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
   </si>
   <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
@@ -283,76 +283,76 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Slavia Praha II</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Slavia Praha II</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
     <t>Stabæk</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Opava</t>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>Shkendija</t>
   </si>
   <si>
-    <t>Rijeka</t>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Artsakh</t>
   </si>
   <si>
     <t>Paphos</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Artsakh</t>
   </si>
   <si>
     <t>Raufoss</t>
@@ -1102,10 +1102,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -1218,7 +1218,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1334,7 +1334,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1450,10 +1450,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -1566,7 +1566,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1801,7 +1801,7 @@
         <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M10">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N10">
+        <v>2.55</v>
+      </c>
+      <c r="O10">
+        <v>1.79</v>
+      </c>
+      <c r="P10">
+        <v>20.5</v>
+      </c>
+      <c r="Q10">
         <v>2.01</v>
       </c>
-      <c r="O10">
-        <v>2.25</v>
-      </c>
-      <c r="P10">
-        <v>14.75</v>
-      </c>
-      <c r="Q10">
-        <v>1.69</v>
-      </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="U10">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Z10">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AA10">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AC10">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD10">
-        <v>2.53</v>
+        <v>2.05</v>
       </c>
       <c r="AE10">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG10">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AH10">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AI10">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -1914,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>67</v>
@@ -2030,7 +2030,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -2057,76 +2057,76 @@
         <v>120</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="s">
         <v>121</v>
@@ -2146,7 +2146,7 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -2173,76 +2173,76 @@
         <v>120</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="s">
         <v>121</v>
@@ -2265,7 +2265,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>2.01</v>
       </c>
       <c r="O14">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="P14">
-        <v>18.5</v>
+        <v>14.75</v>
       </c>
       <c r="Q14">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V14">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AA14">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB14">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AE14">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AH14">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="AI14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2381,7 +2381,7 @@
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="M15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N15">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="P15">
-        <v>16.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q15">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T15">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="U15">
+        <v>1.5</v>
+      </c>
+      <c r="V15">
+        <v>5.85</v>
+      </c>
+      <c r="W15">
+        <v>1.11</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>1.22</v>
+      </c>
+      <c r="AA15">
+        <v>3.8</v>
+      </c>
+      <c r="AB15">
+        <v>1.7</v>
+      </c>
+      <c r="AC15">
+        <v>2.05</v>
+      </c>
+      <c r="AD15">
+        <v>2.62</v>
+      </c>
+      <c r="AE15">
+        <v>1.42</v>
+      </c>
+      <c r="AF15">
         <v>1.57</v>
       </c>
-      <c r="V15">
-        <v>5</v>
-      </c>
-      <c r="W15">
-        <v>1.13</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>11</v>
-      </c>
-      <c r="Z15">
-        <v>1.12</v>
-      </c>
-      <c r="AA15">
-        <v>4.33</v>
-      </c>
-      <c r="AB15">
-        <v>1.53</v>
-      </c>
-      <c r="AC15">
-        <v>2.2</v>
-      </c>
-      <c r="AD15">
-        <v>2.4</v>
-      </c>
-      <c r="AE15">
-        <v>1.5</v>
-      </c>
-      <c r="AF15">
-        <v>1.5</v>
-      </c>
       <c r="AG15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH15">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AI15">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2494,7 +2494,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -2521,76 +2521,76 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2613,7 +2613,7 @@
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -2726,7 +2726,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
         <v>57</v>
@@ -2753,76 +2753,76 @@
         <v>120</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ18" t="s">
         <v>121</v>
@@ -2845,7 +2845,7 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -2878,31 +2878,31 @@
         <v>20</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -2911,28 +2911,28 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH19">
         <v>1.95</v>
@@ -2961,7 +2961,7 @@
         <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>76</v>
@@ -3077,7 +3077,7 @@
         <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -3101,76 +3101,76 @@
         <v>120</v>
       </c>
       <c r="L21">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
+        <v>1.68</v>
+      </c>
+      <c r="P21">
+        <v>7.75</v>
+      </c>
+      <c r="Q21">
+        <v>2.55</v>
+      </c>
+      <c r="R21">
+        <v>1.43</v>
+      </c>
+      <c r="S21">
+        <v>2.6</v>
+      </c>
+      <c r="T21">
+        <v>2.95</v>
+      </c>
+      <c r="U21">
+        <v>1.34</v>
+      </c>
+      <c r="V21">
+        <v>7.75</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>7.1</v>
+      </c>
+      <c r="Z21">
+        <v>1.32</v>
+      </c>
+      <c r="AA21">
+        <v>2.97</v>
+      </c>
+      <c r="AB21">
+        <v>2.1</v>
+      </c>
+      <c r="AC21">
+        <v>1.67</v>
+      </c>
+      <c r="AD21">
+        <v>3.48</v>
+      </c>
+      <c r="AE21">
         <v>1.24</v>
       </c>
-      <c r="P21">
-        <v>19.75</v>
-      </c>
-      <c r="Q21">
-        <v>4.25</v>
-      </c>
-      <c r="R21">
-        <v>1.21</v>
-      </c>
-      <c r="S21">
-        <v>3.58</v>
-      </c>
-      <c r="T21">
-        <v>2.14</v>
-      </c>
-      <c r="U21">
-        <v>1.63</v>
-      </c>
-      <c r="V21">
-        <v>4.4</v>
-      </c>
-      <c r="W21">
-        <v>1.14</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>20</v>
-      </c>
-      <c r="Z21">
-        <v>1.11</v>
-      </c>
-      <c r="AA21">
-        <v>4.8</v>
-      </c>
-      <c r="AB21">
-        <v>1.6</v>
-      </c>
-      <c r="AC21">
-        <v>2.2</v>
-      </c>
-      <c r="AD21">
-        <v>2.4</v>
-      </c>
-      <c r="AE21">
-        <v>1.5</v>
-      </c>
       <c r="AF21">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG21">
         <v>1.75</v>
       </c>
       <c r="AH21">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI21">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="s">
         <v>121</v>
@@ -3193,7 +3193,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -3217,76 +3217,76 @@
         <v>120</v>
       </c>
       <c r="L22">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P22">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q22">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R22">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T22">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V22">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z22">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA22">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG22">
         <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI22">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ22" t="s">
         <v>121</v>
@@ -3309,7 +3309,7 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M23">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S23">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V23">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z23">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA23">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AE23">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH23">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3425,7 +3425,7 @@
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="M24">
+        <v>4.5</v>
+      </c>
+      <c r="N24">
+        <v>6.5</v>
+      </c>
+      <c r="O24">
+        <v>1.33</v>
+      </c>
+      <c r="P24">
+        <v>13.5</v>
+      </c>
+      <c r="Q24">
         <v>3.5</v>
       </c>
-      <c r="N24">
-        <v>3.5</v>
-      </c>
-      <c r="O24">
-        <v>1.6</v>
-      </c>
-      <c r="P24">
-        <v>10</v>
-      </c>
-      <c r="Q24">
-        <v>2.55</v>
-      </c>
       <c r="R24">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U24">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="V24">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="Z24">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AA24">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD24">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH24">
-        <v>5.5</v>
+        <v>3.72</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3541,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>81</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M25">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="P25">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T25">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>19.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z25">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AA25">
-        <v>4.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AD25">
-        <v>2.33</v>
+        <v>3.32</v>
       </c>
       <c r="AE25">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AF25">
         <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH25">
-        <v>3.72</v>
+        <v>6.4</v>
       </c>
       <c r="AI25">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3657,7 +3657,7 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
@@ -3773,7 +3773,7 @@
         <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -3889,7 +3889,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -4005,7 +4005,7 @@
         <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -4118,10 +4118,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
         <v>86</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
         <v>88</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -199,69 +199,69 @@
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
+    <t>Malmö FF</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>FCSB</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
     <t>Panathinaikos</t>
   </si>
   <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
@@ -292,67 +292,67 @@
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Start</t>
+    <t>Rīgas FS</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
     <t>Shkendija</t>
   </si>
   <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Artsakh</t>
+  </si>
+  <si>
     <t>Rangers</t>
-  </si>
-  <si>
-    <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Paphos</t>
   </si>
   <si>
     <t>Raufoss</t>
@@ -1218,10 +1218,10 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1334,10 +1334,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1566,10 +1566,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>64</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,10 +1682,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>65</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="M10">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N10">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="P10">
-        <v>20.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q10">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AB10">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD10">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AE10">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AF10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH10">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AI10">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -2030,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
@@ -2057,76 +2057,76 @@
         <v>120</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>121</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -2173,76 +2173,76 @@
         <v>120</v>
       </c>
       <c r="L13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="s">
         <v>121</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M14">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N14">
+        <v>2.55</v>
+      </c>
+      <c r="O14">
+        <v>1.79</v>
+      </c>
+      <c r="P14">
+        <v>20.5</v>
+      </c>
+      <c r="Q14">
         <v>2.01</v>
       </c>
-      <c r="O14">
-        <v>2.25</v>
-      </c>
-      <c r="P14">
-        <v>14.75</v>
-      </c>
-      <c r="Q14">
-        <v>1.69</v>
-      </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="S14">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T14">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="U14">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V14">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="Z14">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AA14">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="AD14">
-        <v>2.53</v>
+        <v>2.05</v>
       </c>
       <c r="AE14">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AH14">
-        <v>4.6</v>
+        <v>3.22</v>
       </c>
       <c r="AI14">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2378,10 +2378,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>2.9</v>
+        <v>1.14</v>
       </c>
       <c r="M15">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="N15">
+        <v>18</v>
+      </c>
+      <c r="O15">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>17</v>
+      </c>
+      <c r="Q15">
+        <v>4.8</v>
+      </c>
+      <c r="R15">
+        <v>1.22</v>
+      </c>
+      <c r="S15">
+        <v>3.9</v>
+      </c>
+      <c r="T15">
+        <v>1.98</v>
+      </c>
+      <c r="U15">
+        <v>1.71</v>
+      </c>
+      <c r="V15">
+        <v>4.2</v>
+      </c>
+      <c r="W15">
+        <v>1.2</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>17.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.14</v>
+      </c>
+      <c r="AA15">
+        <v>5.25</v>
+      </c>
+      <c r="AB15">
+        <v>1.4</v>
+      </c>
+      <c r="AC15">
+        <v>2.75</v>
+      </c>
+      <c r="AD15">
         <v>2.25</v>
       </c>
-      <c r="O15">
-        <v>2.12</v>
-      </c>
-      <c r="P15">
-        <v>13.25</v>
-      </c>
-      <c r="Q15">
-        <v>1.8</v>
-      </c>
-      <c r="R15">
-        <v>1.3</v>
-      </c>
-      <c r="S15">
-        <v>3.1</v>
-      </c>
-      <c r="T15">
-        <v>2.47</v>
-      </c>
-      <c r="U15">
-        <v>1.5</v>
-      </c>
-      <c r="V15">
-        <v>5.85</v>
-      </c>
-      <c r="W15">
-        <v>1.11</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>10</v>
-      </c>
-      <c r="Z15">
-        <v>1.22</v>
-      </c>
-      <c r="AA15">
-        <v>3.8</v>
-      </c>
-      <c r="AB15">
-        <v>1.7</v>
-      </c>
-      <c r="AC15">
-        <v>2.05</v>
-      </c>
-      <c r="AD15">
-        <v>2.62</v>
-      </c>
       <c r="AE15">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AI15">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2494,10 +2494,10 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>72</v>
@@ -2521,76 +2521,76 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2610,10 +2610,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -2637,76 +2637,76 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
       <c r="M17">
-        <v>7.4</v>
+        <v>3.46</v>
       </c>
       <c r="N17">
-        <v>18</v>
+        <v>2.55</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q17">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="R17">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T17">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="U17">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="V17">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>17.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z17">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AA17">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE17">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG17">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AH17">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AI17">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -2726,10 +2726,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
@@ -2753,76 +2753,76 @@
         <v>120</v>
       </c>
       <c r="L18">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="s">
         <v>121</v>
@@ -2842,10 +2842,10 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -2869,76 +2869,76 @@
         <v>120</v>
       </c>
       <c r="L19">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="Q19">
+        <v>3.9</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.6</v>
+      </c>
+      <c r="T19">
+        <v>2.15</v>
+      </c>
+      <c r="U19">
+        <v>1.62</v>
+      </c>
+      <c r="V19">
         <v>4.6</v>
       </c>
-      <c r="R19">
-        <v>1.13</v>
-      </c>
-      <c r="S19">
-        <v>5.25</v>
-      </c>
-      <c r="T19">
+      <c r="W19">
+        <v>1.16</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>19.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.1</v>
+      </c>
+      <c r="AA19">
+        <v>5.15</v>
+      </c>
+      <c r="AB19">
         <v>1.6</v>
       </c>
-      <c r="U19">
-        <v>2.15</v>
-      </c>
-      <c r="V19">
-        <v>2.87</v>
-      </c>
-      <c r="W19">
-        <v>1.36</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>1.01</v>
-      </c>
-      <c r="AA19">
-        <v>10</v>
-      </c>
-      <c r="AB19">
-        <v>1.2</v>
-      </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE19">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH19">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="AI19">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="s">
         <v>121</v>
@@ -2958,10 +2958,10 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
         <v>76</v>
@@ -2985,76 +2985,76 @@
         <v>120</v>
       </c>
       <c r="L20">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q20">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S20">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T20">
+        <v>1.6</v>
+      </c>
+      <c r="U20">
         <v>2.15</v>
       </c>
-      <c r="U20">
-        <v>1.62</v>
-      </c>
       <c r="V20">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
         <v>1.01</v>
       </c>
-      <c r="Y20">
-        <v>19.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.1</v>
-      </c>
       <c r="AA20">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC20">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD20">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE20">
+        <v>2.45</v>
+      </c>
+      <c r="AF20">
         <v>1.73</v>
       </c>
-      <c r="AF20">
-        <v>1.9</v>
-      </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH20">
-        <v>3.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI20">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="s">
         <v>121</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S23">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V23">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z23">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA23">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD23">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH23">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M25">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S25">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T25">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V25">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z25">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA25">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB25">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC25">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AE25">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH25">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI25">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3681,13 +3681,13 @@
         <v>120</v>
       </c>
       <c r="L26">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="M26">
-        <v>6.36</v>
+        <v>7.02</v>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O26">
         <v>1.25</v>
@@ -3699,55 +3699,55 @@
         <v>3.92</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T26">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V26">
         <v>4</v>
       </c>
       <c r="W26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Z26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AA26">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AB26">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AI26">
         <v>1.29</v>
@@ -3806,43 +3806,43 @@
         <v>1.65</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>1.73</v>
@@ -3851,22 +3851,22 @@
         <v>2</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AJ27" t="s">
         <v>121</v>
@@ -4261,13 +4261,13 @@
         <v>120</v>
       </c>
       <c r="L31">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N31">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="O31">
         <v>1.95</v>
@@ -4279,7 +4279,7 @@
         <v>1.91</v>
       </c>
       <c r="R31">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
         <v>3.1</v>
@@ -4291,7 +4291,7 @@
         <v>1.45</v>
       </c>
       <c r="V31">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W31">
         <v>1.1</v>
@@ -4309,7 +4309,7 @@
         <v>3.7</v>
       </c>
       <c r="AB31">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
         <v>1.97</v>
@@ -4321,7 +4321,7 @@
         <v>1.33</v>
       </c>
       <c r="AF31">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
         <v>2.14</v>
@@ -4377,13 +4377,13 @@
         <v>120</v>
       </c>
       <c r="L32">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M32">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N32">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O32">
         <v>1.62</v>
@@ -4395,22 +4395,22 @@
         <v>2.5</v>
       </c>
       <c r="R32">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S32">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T32">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -4425,13 +4425,13 @@
         <v>3.5</v>
       </c>
       <c r="AB32">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
         <v>1.85</v>
       </c>
       <c r="AD32">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AE32">
         <v>1.32</v>
@@ -4443,7 +4443,7 @@
         <v>1.97</v>
       </c>
       <c r="AH32">
-        <v>6.35</v>
+        <v>5.5</v>
       </c>
       <c r="AI32">
         <v>1.11</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -166,12 +166,12 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -184,63 +184,63 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025/2026</t>
   </si>
   <si>
-    <t>2025</t>
+    <t>New England II</t>
   </si>
   <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
     <t>Skeid</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
+    <t>Prostějov</t>
   </si>
   <si>
     <t>Hødd</t>
   </si>
   <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -253,18 +253,18 @@
     <t>FCSB</t>
   </si>
   <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Panathinaikos</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -283,57 +283,57 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
     <t>Aalesund</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Åsane</t>
+    <t>Opava</t>
   </si>
   <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
@@ -346,16 +346,16 @@
     <t>Shkendija</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
     <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
   </si>
   <si>
     <t>Lech Poznań</t>
@@ -1102,10 +1102,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -1221,7 +1221,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1245,22 +1245,22 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="M5">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="N5">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="P5">
-        <v>13.25</v>
+        <v>16.5</v>
       </c>
       <c r="Q5">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1269,52 +1269,52 @@
         <v>3.1</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U5">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="Z5">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AA5">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AE5">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AI5">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1337,7 +1337,7 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="M6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N6">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="P6">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U6">
         <v>1.5</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>13</v>
       </c>
       <c r="Z6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA6">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="AB6">
         <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AD6">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AE6">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH6">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AI6">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1450,7 +1450,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1477,76 +1477,76 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1569,7 +1569,7 @@
         <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>64</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>1.75</v>
+        <v>2.94</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="P8">
-        <v>18.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q8">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V8">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>13.8</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA8">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AB8">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AD8">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AE8">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH8">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="AI8">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>3.25</v>
+        <v>1.14</v>
       </c>
       <c r="M9">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>18</v>
       </c>
       <c r="O9">
+        <v>1.2</v>
+      </c>
+      <c r="P9">
+        <v>17</v>
+      </c>
+      <c r="Q9">
+        <v>4.8</v>
+      </c>
+      <c r="R9">
+        <v>1.22</v>
+      </c>
+      <c r="S9">
+        <v>3.9</v>
+      </c>
+      <c r="T9">
+        <v>1.98</v>
+      </c>
+      <c r="U9">
+        <v>1.71</v>
+      </c>
+      <c r="V9">
+        <v>4.2</v>
+      </c>
+      <c r="W9">
+        <v>1.2</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>17.5</v>
+      </c>
+      <c r="Z9">
+        <v>1.14</v>
+      </c>
+      <c r="AA9">
+        <v>5.25</v>
+      </c>
+      <c r="AB9">
+        <v>1.4</v>
+      </c>
+      <c r="AC9">
+        <v>2.75</v>
+      </c>
+      <c r="AD9">
         <v>2.25</v>
       </c>
-      <c r="P9">
-        <v>14.75</v>
-      </c>
-      <c r="Q9">
-        <v>1.69</v>
-      </c>
-      <c r="R9">
+      <c r="AE9">
+        <v>1.6</v>
+      </c>
+      <c r="AF9">
+        <v>2.1</v>
+      </c>
+      <c r="AG9">
+        <v>1.65</v>
+      </c>
+      <c r="AH9">
+        <v>3.3</v>
+      </c>
+      <c r="AI9">
         <v>1.29</v>
-      </c>
-      <c r="S9">
-        <v>3.28</v>
-      </c>
-      <c r="T9">
-        <v>2.45</v>
-      </c>
-      <c r="U9">
-        <v>1.5</v>
-      </c>
-      <c r="V9">
-        <v>5.8</v>
-      </c>
-      <c r="W9">
-        <v>1.13</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>13</v>
-      </c>
-      <c r="Z9">
-        <v>1.15</v>
-      </c>
-      <c r="AA9">
-        <v>4.2</v>
-      </c>
-      <c r="AB9">
-        <v>1.67</v>
-      </c>
-      <c r="AC9">
-        <v>2.16</v>
-      </c>
-      <c r="AD9">
-        <v>2.53</v>
-      </c>
-      <c r="AE9">
-        <v>1.41</v>
-      </c>
-      <c r="AF9">
-        <v>1.57</v>
-      </c>
-      <c r="AG9">
-        <v>2.3</v>
-      </c>
-      <c r="AH9">
-        <v>4.6</v>
-      </c>
-      <c r="AI9">
-        <v>1.16</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1798,7 +1798,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -1914,7 +1914,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -1941,76 +1941,76 @@
         <v>120</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -2265,7 +2265,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
+        <v>2.8</v>
+      </c>
+      <c r="M14">
+        <v>3.5</v>
+      </c>
+      <c r="N14">
+        <v>2.26</v>
+      </c>
+      <c r="O14">
+        <v>2.16</v>
+      </c>
+      <c r="P14">
+        <v>15</v>
+      </c>
+      <c r="Q14">
+        <v>1.74</v>
+      </c>
+      <c r="R14">
+        <v>1.3</v>
+      </c>
+      <c r="S14">
+        <v>3.1</v>
+      </c>
+      <c r="T14">
         <v>2.3</v>
       </c>
-      <c r="M14">
-        <v>3.9</v>
-      </c>
-      <c r="N14">
-        <v>2.55</v>
-      </c>
-      <c r="O14">
-        <v>1.79</v>
-      </c>
-      <c r="P14">
-        <v>20.5</v>
-      </c>
-      <c r="Q14">
-        <v>2.01</v>
-      </c>
-      <c r="R14">
-        <v>1.21</v>
-      </c>
-      <c r="S14">
-        <v>3.75</v>
-      </c>
-      <c r="T14">
-        <v>2.12</v>
-      </c>
       <c r="U14">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V14">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z14">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>5.75</v>
+        <v>4.48</v>
       </c>
       <c r="AB14">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="AD14">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="AE14">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AF14">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH14">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="AI14">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2378,10 +2378,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2494,10 +2494,10 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
         <v>72</v>
@@ -2613,7 +2613,7 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -2637,76 +2637,76 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="M17">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="N17">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="P17">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q17">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R17">
         <v>1.3</v>
       </c>
       <c r="S17">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="U17">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AA17">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="AB17">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD17">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE17">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF17">
         <v>1.5</v>
       </c>
       <c r="AG17">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH17">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AI17">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -2726,10 +2726,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
@@ -2845,7 +2845,7 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -2961,7 +2961,7 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>76</v>
@@ -3077,7 +3077,7 @@
         <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -3193,7 +3193,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -3309,7 +3309,7 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M23">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S23">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V23">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z23">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA23">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AE23">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH23">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3422,7 +3422,7 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="M24">
-        <v>4.5</v>
+        <v>7.02</v>
       </c>
       <c r="N24">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="O24">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P24">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R24">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S24">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T24">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U24">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA24">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC24">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD24">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AE24">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF24">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AG24">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH24">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AI24">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3541,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
         <v>81</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S25">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V25">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z25">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA25">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE25">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH25">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI25">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3654,7 +3654,7 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
         <v>57</v>
@@ -3681,76 +3681,76 @@
         <v>120</v>
       </c>
       <c r="L26">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>7.02</v>
+        <v>4.5</v>
       </c>
       <c r="N26">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P26">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q26">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U26">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AA26">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="AB26">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD26">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AE26">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF26">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH26">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AI26">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AJ26" t="s">
         <v>121</v>
@@ -3773,7 +3773,7 @@
         <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -3889,7 +3889,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -4005,7 +4005,7 @@
         <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -4118,10 +4118,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
         <v>86</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -4264,10 +4264,10 @@
         <v>2.5</v>
       </c>
       <c r="M31">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="N31">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
         <v>1.95</v>
@@ -4279,58 +4279,58 @@
         <v>1.91</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T31">
         <v>2.5</v>
       </c>
       <c r="U31">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V31">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="Z31">
         <v>1.22</v>
       </c>
       <c r="AA31">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB31">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC31">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD31">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AE31">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF31">
         <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH31">
         <v>5.25</v>
       </c>
       <c r="AI31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ31" t="s">
         <v>121</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
         <v>88</v>
@@ -4377,13 +4377,13 @@
         <v>120</v>
       </c>
       <c r="L32">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="M32">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N32">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="O32">
         <v>1.62</v>
@@ -4401,7 +4401,7 @@
         <v>2.65</v>
       </c>
       <c r="T32">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="U32">
         <v>1.4</v>
@@ -4416,31 +4416,31 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>9.449999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z32">
         <v>1.24</v>
       </c>
       <c r="AA32">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD32">
         <v>3.2</v>
       </c>
       <c r="AE32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG32">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AH32">
         <v>5.5</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -199,48 +199,48 @@
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
     <t>Odd</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
     <t>Vyškov</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -256,15 +256,15 @@
     <t>Panathinaikos</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -292,48 +292,48 @@
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Sogndal</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
     <t>Åsane</t>
   </si>
   <si>
     <t>Stabæk</t>
   </si>
   <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
@@ -349,13 +349,13 @@
     <t>Rangers</t>
   </si>
   <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Artsakh</t>
+  </si>
+  <si>
     <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Artsakh</t>
   </si>
   <si>
     <t>Lech Poznań</t>
@@ -1218,10 +1218,10 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="M6">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N6">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="P6">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="Q6">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="U6">
         <v>1.5</v>
       </c>
       <c r="V6">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
         <v>13</v>
       </c>
       <c r="Z6">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD6">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH6">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AI6">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1450,10 +1450,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -1477,76 +1477,76 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="M7">
+        <v>7.4</v>
+      </c>
+      <c r="N7">
+        <v>18</v>
+      </c>
+      <c r="O7">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>17</v>
+      </c>
+      <c r="Q7">
+        <v>4.8</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
         <v>3.9</v>
       </c>
-      <c r="N7">
-        <v>2.55</v>
-      </c>
-      <c r="O7">
-        <v>1.79</v>
-      </c>
-      <c r="P7">
-        <v>20.5</v>
-      </c>
-      <c r="Q7">
-        <v>2.01</v>
-      </c>
-      <c r="R7">
-        <v>1.21</v>
-      </c>
-      <c r="S7">
-        <v>3.75</v>
-      </c>
       <c r="T7">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AA7">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AB7">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH7">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AI7">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1798,10 +1798,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -2289,22 +2289,22 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="M14">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="N14">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="O14">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="P14">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Q14">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="R14">
         <v>1.3</v>
@@ -2313,52 +2313,52 @@
         <v>3.1</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U14">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Z14">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA14">
-        <v>4.48</v>
+        <v>4.65</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
         <v>2.2</v>
       </c>
       <c r="AD14">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AE14">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF14">
         <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH14">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AI14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2494,10 +2494,10 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>72</v>
@@ -2521,76 +2521,76 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2637,76 +2637,76 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="M17">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N17">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O17">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="P17">
-        <v>15.75</v>
+        <v>20.5</v>
       </c>
       <c r="Q17">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="R17">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T17">
-        <v>2.52</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z17">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AA17">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AC17">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="AD17">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE17">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AF17">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="AI17">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -3422,10 +3422,10 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>1.14</v>
+        <v>1.89</v>
       </c>
       <c r="M24">
-        <v>7.02</v>
+        <v>3.35</v>
       </c>
       <c r="N24">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="P24">
-        <v>20.5</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>3.92</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S24">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T24">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>7.25</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="Z24">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AA24">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB24">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD24">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AE24">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG24">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AH24">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI24">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M25">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O25">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S25">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V25">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z25">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA25">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB25">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE25">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF25">
         <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH25">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI25">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3654,10 +3654,10 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
@@ -3681,76 +3681,76 @@
         <v>120</v>
       </c>
       <c r="L26">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="M26">
-        <v>4.5</v>
+        <v>7.02</v>
       </c>
       <c r="N26">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P26">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R26">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T26">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA26">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AB26">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC26">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF26">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH26">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AI26">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="s">
         <v>121</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -166,105 +166,105 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
+    <t>Europe UEFA Champions League</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Europe UEFA Champions League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025/2026</t>
+    <t>Sparta Praha II</t>
   </si>
   <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
+    <t>FK Bodo - Glimt</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
+    <t>FCSB</t>
   </si>
   <si>
     <t>Ludogorets</t>
   </si>
   <si>
-    <t>FCSB</t>
+    <t>Maccabi Tel Aviv</t>
   </si>
   <si>
     <t>Panathinaikos</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
+    <t>Lillestrøm</t>
   </si>
   <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -283,79 +283,79 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Slavia Praha II</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Slavia Praha II</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
+    <t>Strømsgodset</t>
   </si>
   <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Strømsgodset</t>
+    <t>Shkendija</t>
   </si>
   <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Shkendija</t>
+    <t>Paphos</t>
   </si>
   <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Paphos</t>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
   </si>
   <si>
     <t>Lech Poznań</t>
@@ -1102,10 +1102,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -1218,10 +1218,10 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1334,10 +1334,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -1361,31 +1361,31 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="M6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="P6">
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
         <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
         <v>1.5</v>
@@ -1394,10 +1394,10 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>13</v>
@@ -1406,31 +1406,31 @@
         <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD6">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="AE6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF6">
         <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AI6">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1477,76 +1477,76 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
       <c r="M7">
-        <v>7.4</v>
+        <v>3.46</v>
       </c>
       <c r="N7">
-        <v>18</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q7">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="U7">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="V7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AA7">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AB7">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC7">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD7">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE7">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AH7">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AI7">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1566,7 +1566,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1798,10 +1798,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
@@ -1825,64 +1825,64 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="M10">
         <v>3.5</v>
       </c>
       <c r="N10">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="P10">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Q10">
-        <v>1.74</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="U10">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="Z10">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA10">
-        <v>4.48</v>
+        <v>4.9</v>
       </c>
       <c r="AB10">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD10">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AE10">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AF10">
         <v>1.5</v>
@@ -1891,10 +1891,10 @@
         <v>2.4</v>
       </c>
       <c r="AH10">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AI10">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -1914,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>67</v>
@@ -1941,76 +1941,76 @@
         <v>120</v>
       </c>
       <c r="L11">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M11">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="P11">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q11">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T11">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>13.8</v>
+        <v>19</v>
       </c>
       <c r="Z11">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AA11">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="AB11">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC11">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AD11">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AE11">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH11">
-        <v>3.94</v>
+        <v>3.22</v>
       </c>
       <c r="AI11">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -2262,10 +2262,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,22 +2289,22 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="M14">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N14">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O14">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="P14">
-        <v>16.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R14">
         <v>1.3</v>
@@ -2313,52 +2313,52 @@
         <v>3.1</v>
       </c>
       <c r="T14">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U14">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="V14">
+        <v>6</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>1.2</v>
+      </c>
+      <c r="AA14">
+        <v>4</v>
+      </c>
+      <c r="AB14">
+        <v>1.65</v>
+      </c>
+      <c r="AC14">
+        <v>2.1</v>
+      </c>
+      <c r="AD14">
+        <v>2.65</v>
+      </c>
+      <c r="AE14">
+        <v>1.42</v>
+      </c>
+      <c r="AF14">
+        <v>1.6</v>
+      </c>
+      <c r="AG14">
+        <v>2.25</v>
+      </c>
+      <c r="AH14">
         <v>5</v>
       </c>
-      <c r="W14">
-        <v>1.15</v>
-      </c>
-      <c r="X14">
-        <v>1</v>
-      </c>
-      <c r="Y14">
-        <v>12.8</v>
-      </c>
-      <c r="Z14">
-        <v>1.12</v>
-      </c>
-      <c r="AA14">
-        <v>4.65</v>
-      </c>
-      <c r="AB14">
-        <v>1.53</v>
-      </c>
-      <c r="AC14">
-        <v>2.2</v>
-      </c>
-      <c r="AD14">
-        <v>2.5</v>
-      </c>
-      <c r="AE14">
-        <v>1.5</v>
-      </c>
-      <c r="AF14">
-        <v>1.5</v>
-      </c>
-      <c r="AG14">
-        <v>2.45</v>
-      </c>
-      <c r="AH14">
-        <v>4.5</v>
-      </c>
       <c r="AI14">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2378,7 +2378,7 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2494,7 +2494,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>56</v>
@@ -2521,76 +2521,76 @@
         <v>120</v>
       </c>
       <c r="L16">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="s">
         <v>121</v>
@@ -2610,7 +2610,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
@@ -2637,76 +2637,76 @@
         <v>120</v>
       </c>
       <c r="L17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="s">
         <v>121</v>
@@ -2726,10 +2726,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
@@ -2842,7 +2842,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
         <v>57</v>
@@ -2869,76 +2869,76 @@
         <v>120</v>
       </c>
       <c r="L19">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O19">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P19">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q19">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S19">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T19">
+        <v>1.6</v>
+      </c>
+      <c r="U19">
         <v>2.15</v>
       </c>
-      <c r="U19">
-        <v>1.62</v>
-      </c>
       <c r="V19">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
         <v>1.01</v>
       </c>
-      <c r="Y19">
-        <v>19.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.1</v>
-      </c>
       <c r="AA19">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE19">
+        <v>2.45</v>
+      </c>
+      <c r="AF19">
         <v>1.73</v>
       </c>
-      <c r="AF19">
-        <v>1.9</v>
-      </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH19">
-        <v>3.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI19">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AJ19" t="s">
         <v>121</v>
@@ -2958,7 +2958,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2985,76 +2985,76 @@
         <v>120</v>
       </c>
       <c r="L20">
+        <v>1.35</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20">
+        <v>8</v>
+      </c>
+      <c r="O20">
+        <v>1.27</v>
+      </c>
+      <c r="P20">
+        <v>15.5</v>
+      </c>
+      <c r="Q20">
+        <v>3.9</v>
+      </c>
+      <c r="R20">
+        <v>1.25</v>
+      </c>
+      <c r="S20">
+        <v>3.6</v>
+      </c>
+      <c r="T20">
+        <v>2.15</v>
+      </c>
+      <c r="U20">
+        <v>1.62</v>
+      </c>
+      <c r="V20">
+        <v>4.6</v>
+      </c>
+      <c r="W20">
+        <v>1.16</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>19.5</v>
+      </c>
+      <c r="Z20">
         <v>1.1</v>
       </c>
-      <c r="M20">
-        <v>8</v>
-      </c>
-      <c r="N20">
-        <v>11</v>
-      </c>
-      <c r="O20">
-        <v>1.18</v>
-      </c>
-      <c r="P20">
-        <v>29</v>
-      </c>
-      <c r="Q20">
-        <v>4.6</v>
-      </c>
-      <c r="R20">
-        <v>1.13</v>
-      </c>
-      <c r="S20">
-        <v>5.25</v>
-      </c>
-      <c r="T20">
+      <c r="AA20">
+        <v>5.15</v>
+      </c>
+      <c r="AB20">
         <v>1.6</v>
       </c>
-      <c r="U20">
-        <v>2.15</v>
-      </c>
-      <c r="V20">
-        <v>2.87</v>
-      </c>
-      <c r="W20">
-        <v>1.36</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>1.01</v>
-      </c>
-      <c r="AA20">
-        <v>10</v>
-      </c>
-      <c r="AB20">
-        <v>1.2</v>
-      </c>
       <c r="AC20">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD20">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE20">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH20">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="AI20">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AJ20" t="s">
         <v>121</v>
@@ -3074,10 +3074,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -3101,76 +3101,76 @@
         <v>120</v>
       </c>
       <c r="L21">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P21">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q21">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R21">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S21">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T21">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U21">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z21">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA21">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE21">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG21">
         <v>1.75</v>
       </c>
       <c r="AH21">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI21">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="s">
         <v>121</v>
@@ -3190,10 +3190,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -3217,76 +3217,76 @@
         <v>120</v>
       </c>
       <c r="L22">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
+        <v>1.68</v>
+      </c>
+      <c r="P22">
+        <v>7.75</v>
+      </c>
+      <c r="Q22">
+        <v>2.55</v>
+      </c>
+      <c r="R22">
+        <v>1.43</v>
+      </c>
+      <c r="S22">
+        <v>2.6</v>
+      </c>
+      <c r="T22">
+        <v>2.95</v>
+      </c>
+      <c r="U22">
+        <v>1.34</v>
+      </c>
+      <c r="V22">
+        <v>7.75</v>
+      </c>
+      <c r="W22">
+        <v>1.07</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
+        <v>7.1</v>
+      </c>
+      <c r="Z22">
+        <v>1.32</v>
+      </c>
+      <c r="AA22">
+        <v>2.97</v>
+      </c>
+      <c r="AB22">
+        <v>2.1</v>
+      </c>
+      <c r="AC22">
+        <v>1.67</v>
+      </c>
+      <c r="AD22">
+        <v>3.48</v>
+      </c>
+      <c r="AE22">
         <v>1.24</v>
       </c>
-      <c r="P22">
-        <v>19.75</v>
-      </c>
-      <c r="Q22">
-        <v>4.25</v>
-      </c>
-      <c r="R22">
-        <v>1.21</v>
-      </c>
-      <c r="S22">
-        <v>3.58</v>
-      </c>
-      <c r="T22">
-        <v>2.14</v>
-      </c>
-      <c r="U22">
-        <v>1.63</v>
-      </c>
-      <c r="V22">
-        <v>4.4</v>
-      </c>
-      <c r="W22">
-        <v>1.14</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>20</v>
-      </c>
-      <c r="Z22">
-        <v>1.11</v>
-      </c>
-      <c r="AA22">
-        <v>4.8</v>
-      </c>
-      <c r="AB22">
-        <v>1.6</v>
-      </c>
-      <c r="AC22">
-        <v>2.2</v>
-      </c>
-      <c r="AD22">
-        <v>2.4</v>
-      </c>
-      <c r="AE22">
-        <v>1.5</v>
-      </c>
       <c r="AF22">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG22">
         <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI22">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ22" t="s">
         <v>121</v>
@@ -3306,10 +3306,10 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S23">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V23">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z23">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA23">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD23">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH23">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3422,10 +3422,10 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="M24">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N24">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S24">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U24">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V24">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z24">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA24">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD24">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AE24">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH24">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI24">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="M25">
-        <v>4.5</v>
+        <v>7.02</v>
       </c>
       <c r="N25">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P25">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q25">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R25">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U25">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA25">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC25">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AE25">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH25">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AI25">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3681,76 +3681,76 @@
         <v>120</v>
       </c>
       <c r="L26">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>7.02</v>
+        <v>4.5</v>
       </c>
       <c r="N26">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P26">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q26">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U26">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AA26">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="AB26">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD26">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AE26">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF26">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH26">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AI26">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AJ26" t="s">
         <v>121</v>
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -3886,10 +3886,10 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -4002,10 +4002,10 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -4118,10 +4118,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
         <v>86</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
         <v>88</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -166,78 +166,78 @@
     <t>23:00</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
+    <t>Norway First Division</t>
   </si>
   <si>
     <t>Europe UEFA Champions League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025/2026</t>
   </si>
   <si>
-    <t>2025</t>
+    <t>New England II</t>
   </si>
   <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Moss</t>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Prostějov</t>
   </si>
   <si>
@@ -247,24 +247,24 @@
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
     <t>FCSB</t>
   </si>
   <si>
-    <t>Ludogorets</t>
+    <t>Ferencváros</t>
   </si>
   <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
     <t>Panathinaikos</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -283,54 +283,54 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Start</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>Aalesund</t>
   </si>
   <si>
-    <t>Sogndal</t>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Opava</t>
   </si>
   <si>
@@ -340,22 +340,22 @@
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>Shkendija</t>
   </si>
   <si>
-    <t>Rijeka</t>
+    <t>Artsakh</t>
   </si>
   <si>
     <t>Paphos</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Rangers</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Artsakh</t>
   </si>
   <si>
     <t>Lech Poznań</t>
@@ -1102,10 +1102,10 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="M5">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="N5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O5">
+        <v>1.61</v>
+      </c>
+      <c r="P5">
+        <v>18.5</v>
+      </c>
+      <c r="Q5">
+        <v>2.33</v>
+      </c>
+      <c r="R5">
+        <v>1.27</v>
+      </c>
+      <c r="S5">
+        <v>3.3</v>
+      </c>
+      <c r="T5">
+        <v>2.23</v>
+      </c>
+      <c r="U5">
+        <v>1.61</v>
+      </c>
+      <c r="V5">
+        <v>4.5</v>
+      </c>
+      <c r="W5">
+        <v>1.15</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>13.8</v>
+      </c>
+      <c r="Z5">
+        <v>1.15</v>
+      </c>
+      <c r="AA5">
+        <v>4.9</v>
+      </c>
+      <c r="AB5">
+        <v>1.47</v>
+      </c>
+      <c r="AC5">
+        <v>2.33</v>
+      </c>
+      <c r="AD5">
+        <v>2.4</v>
+      </c>
+      <c r="AE5">
+        <v>1.53</v>
+      </c>
+      <c r="AF5">
+        <v>1.5</v>
+      </c>
+      <c r="AG5">
+        <v>2.4</v>
+      </c>
+      <c r="AH5">
+        <v>3.94</v>
+      </c>
+      <c r="AI5">
         <v>1.2</v>
-      </c>
-      <c r="P5">
-        <v>17</v>
-      </c>
-      <c r="Q5">
-        <v>4.8</v>
-      </c>
-      <c r="R5">
-        <v>1.22</v>
-      </c>
-      <c r="S5">
-        <v>3.9</v>
-      </c>
-      <c r="T5">
-        <v>1.98</v>
-      </c>
-      <c r="U5">
-        <v>1.71</v>
-      </c>
-      <c r="V5">
-        <v>4.2</v>
-      </c>
-      <c r="W5">
-        <v>1.2</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>17.5</v>
-      </c>
-      <c r="Z5">
-        <v>1.14</v>
-      </c>
-      <c r="AA5">
-        <v>5.25</v>
-      </c>
-      <c r="AB5">
-        <v>1.4</v>
-      </c>
-      <c r="AC5">
-        <v>2.75</v>
-      </c>
-      <c r="AD5">
-        <v>2.25</v>
-      </c>
-      <c r="AE5">
-        <v>1.6</v>
-      </c>
-      <c r="AF5">
-        <v>2.1</v>
-      </c>
-      <c r="AG5">
-        <v>1.65</v>
-      </c>
-      <c r="AH5">
-        <v>3.3</v>
-      </c>
-      <c r="AI5">
-        <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="M6">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="N6">
-        <v>2.26</v>
+        <v>18</v>
       </c>
       <c r="O6">
-        <v>2.16</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="Z6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA6">
-        <v>4.48</v>
+        <v>5.25</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC6">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AE6">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AH6">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AI6">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1450,10 +1450,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -1477,22 +1477,22 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="M7">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N7">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="P7">
-        <v>16.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -1501,52 +1501,52 @@
         <v>3.1</v>
       </c>
       <c r="T7">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U7">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>1.2</v>
+      </c>
+      <c r="AA7">
+        <v>4</v>
+      </c>
+      <c r="AB7">
+        <v>1.65</v>
+      </c>
+      <c r="AC7">
+        <v>2.1</v>
+      </c>
+      <c r="AD7">
+        <v>2.65</v>
+      </c>
+      <c r="AE7">
+        <v>1.42</v>
+      </c>
+      <c r="AF7">
+        <v>1.6</v>
+      </c>
+      <c r="AG7">
+        <v>2.25</v>
+      </c>
+      <c r="AH7">
         <v>5</v>
       </c>
-      <c r="W7">
-        <v>1.15</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>12.8</v>
-      </c>
-      <c r="Z7">
-        <v>1.12</v>
-      </c>
-      <c r="AA7">
-        <v>4.65</v>
-      </c>
-      <c r="AB7">
-        <v>1.53</v>
-      </c>
-      <c r="AC7">
-        <v>2.2</v>
-      </c>
-      <c r="AD7">
-        <v>2.5</v>
-      </c>
-      <c r="AE7">
-        <v>1.5</v>
-      </c>
-      <c r="AF7">
-        <v>1.5</v>
-      </c>
-      <c r="AG7">
-        <v>2.45</v>
-      </c>
-      <c r="AH7">
-        <v>4.5</v>
-      </c>
       <c r="AI7">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1566,7 +1566,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1682,7 +1682,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1709,76 +1709,76 @@
         <v>120</v>
       </c>
       <c r="L9">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>121</v>
@@ -1798,7 +1798,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1825,76 +1825,76 @@
         <v>120</v>
       </c>
       <c r="L10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="s">
         <v>121</v>
@@ -1914,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>67</v>
@@ -1941,76 +1941,76 @@
         <v>120</v>
       </c>
       <c r="L11">
+        <v>3.25</v>
+      </c>
+      <c r="M11">
+        <v>3.55</v>
+      </c>
+      <c r="N11">
+        <v>1.9</v>
+      </c>
+      <c r="O11">
+        <v>2.25</v>
+      </c>
+      <c r="P11">
+        <v>14.75</v>
+      </c>
+      <c r="Q11">
+        <v>1.69</v>
+      </c>
+      <c r="R11">
+        <v>1.29</v>
+      </c>
+      <c r="S11">
+        <v>3.28</v>
+      </c>
+      <c r="T11">
+        <v>2.45</v>
+      </c>
+      <c r="U11">
+        <v>1.5</v>
+      </c>
+      <c r="V11">
+        <v>5.8</v>
+      </c>
+      <c r="W11">
+        <v>1.13</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <v>1.15</v>
+      </c>
+      <c r="AA11">
+        <v>4.2</v>
+      </c>
+      <c r="AB11">
+        <v>1.67</v>
+      </c>
+      <c r="AC11">
+        <v>2.16</v>
+      </c>
+      <c r="AD11">
+        <v>2.53</v>
+      </c>
+      <c r="AE11">
+        <v>1.41</v>
+      </c>
+      <c r="AF11">
+        <v>1.57</v>
+      </c>
+      <c r="AG11">
         <v>2.3</v>
       </c>
-      <c r="M11">
-        <v>3.9</v>
-      </c>
-      <c r="N11">
-        <v>2.55</v>
-      </c>
-      <c r="O11">
-        <v>1.79</v>
-      </c>
-      <c r="P11">
-        <v>20.5</v>
-      </c>
-      <c r="Q11">
-        <v>2.01</v>
-      </c>
-      <c r="R11">
-        <v>1.21</v>
-      </c>
-      <c r="S11">
-        <v>3.75</v>
-      </c>
-      <c r="T11">
-        <v>2.12</v>
-      </c>
-      <c r="U11">
-        <v>1.62</v>
-      </c>
-      <c r="V11">
-        <v>4.4</v>
-      </c>
-      <c r="W11">
+      <c r="AH11">
+        <v>4.6</v>
+      </c>
+      <c r="AI11">
         <v>1.16</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>19</v>
-      </c>
-      <c r="Z11">
-        <v>1.1</v>
-      </c>
-      <c r="AA11">
-        <v>5.75</v>
-      </c>
-      <c r="AB11">
-        <v>1.38</v>
-      </c>
-      <c r="AC11">
-        <v>2.71</v>
-      </c>
-      <c r="AD11">
-        <v>2.05</v>
-      </c>
-      <c r="AE11">
-        <v>1.57</v>
-      </c>
-      <c r="AF11">
-        <v>1.4</v>
-      </c>
-      <c r="AG11">
-        <v>2.8</v>
-      </c>
-      <c r="AH11">
-        <v>3.22</v>
-      </c>
-      <c r="AI11">
-        <v>1.26</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
@@ -2146,7 +2146,7 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -2173,76 +2173,76 @@
         <v>120</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="s">
         <v>121</v>
@@ -2262,10 +2262,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,22 +2289,22 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="M14">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="O14">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="P14">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="Q14">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R14">
         <v>1.3</v>
@@ -2313,49 +2313,49 @@
         <v>3.1</v>
       </c>
       <c r="T14">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD14">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="AE14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH14">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AI14">
         <v>1.14</v>
@@ -2378,10 +2378,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
@@ -2494,10 +2494,10 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
         <v>72</v>
@@ -2610,10 +2610,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -2726,10 +2726,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
@@ -2845,7 +2845,7 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -2958,10 +2958,10 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
         <v>76</v>
@@ -3074,10 +3074,10 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -3101,76 +3101,76 @@
         <v>120</v>
       </c>
       <c r="L21">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
+        <v>1.68</v>
+      </c>
+      <c r="P21">
+        <v>7.75</v>
+      </c>
+      <c r="Q21">
+        <v>2.55</v>
+      </c>
+      <c r="R21">
+        <v>1.43</v>
+      </c>
+      <c r="S21">
+        <v>2.6</v>
+      </c>
+      <c r="T21">
+        <v>2.95</v>
+      </c>
+      <c r="U21">
+        <v>1.34</v>
+      </c>
+      <c r="V21">
+        <v>7.75</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>7.1</v>
+      </c>
+      <c r="Z21">
+        <v>1.32</v>
+      </c>
+      <c r="AA21">
+        <v>2.97</v>
+      </c>
+      <c r="AB21">
+        <v>2.1</v>
+      </c>
+      <c r="AC21">
+        <v>1.67</v>
+      </c>
+      <c r="AD21">
+        <v>3.48</v>
+      </c>
+      <c r="AE21">
         <v>1.24</v>
       </c>
-      <c r="P21">
-        <v>19.75</v>
-      </c>
-      <c r="Q21">
-        <v>4.25</v>
-      </c>
-      <c r="R21">
-        <v>1.21</v>
-      </c>
-      <c r="S21">
-        <v>3.58</v>
-      </c>
-      <c r="T21">
-        <v>2.14</v>
-      </c>
-      <c r="U21">
-        <v>1.63</v>
-      </c>
-      <c r="V21">
-        <v>4.4</v>
-      </c>
-      <c r="W21">
-        <v>1.14</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>20</v>
-      </c>
-      <c r="Z21">
-        <v>1.11</v>
-      </c>
-      <c r="AA21">
-        <v>4.8</v>
-      </c>
-      <c r="AB21">
-        <v>1.6</v>
-      </c>
-      <c r="AC21">
-        <v>2.2</v>
-      </c>
-      <c r="AD21">
-        <v>2.4</v>
-      </c>
-      <c r="AE21">
-        <v>1.5</v>
-      </c>
       <c r="AF21">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG21">
         <v>1.75</v>
       </c>
       <c r="AH21">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI21">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="s">
         <v>121</v>
@@ -3190,10 +3190,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -3217,76 +3217,76 @@
         <v>120</v>
       </c>
       <c r="L22">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P22">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q22">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R22">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T22">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V22">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z22">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA22">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG22">
         <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI22">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ22" t="s">
         <v>121</v>
@@ -3306,10 +3306,10 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M23">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O23">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U23">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V23">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z23">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA23">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC23">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD23">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE23">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF23">
         <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH23">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3422,10 +3422,10 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -3449,76 +3449,76 @@
         <v>120</v>
       </c>
       <c r="L24">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S24">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T24">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V24">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z24">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA24">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD24">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH24">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="s">
         <v>121</v>
@@ -3538,10 +3538,10 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
         <v>81</v>
@@ -3654,10 +3654,10 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
@@ -3681,76 +3681,76 @@
         <v>120</v>
       </c>
       <c r="L26">
+        <v>2.01</v>
+      </c>
+      <c r="M26">
+        <v>3.5</v>
+      </c>
+      <c r="N26">
+        <v>3.5</v>
+      </c>
+      <c r="O26">
+        <v>1.6</v>
+      </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
+      <c r="Q26">
+        <v>2.55</v>
+      </c>
+      <c r="R26">
+        <v>1.34</v>
+      </c>
+      <c r="S26">
+        <v>2.95</v>
+      </c>
+      <c r="T26">
+        <v>2.55</v>
+      </c>
+      <c r="U26">
         <v>1.44</v>
       </c>
-      <c r="M26">
-        <v>4.5</v>
-      </c>
-      <c r="N26">
-        <v>6.5</v>
-      </c>
-      <c r="O26">
-        <v>1.33</v>
-      </c>
-      <c r="P26">
-        <v>13.5</v>
-      </c>
-      <c r="Q26">
-        <v>3.5</v>
-      </c>
-      <c r="R26">
-        <v>1.27</v>
-      </c>
-      <c r="S26">
-        <v>3.4</v>
-      </c>
-      <c r="T26">
-        <v>2.2</v>
-      </c>
-      <c r="U26">
-        <v>1.58</v>
-      </c>
       <c r="V26">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z26">
+        <v>1.2</v>
+      </c>
+      <c r="AA26">
+        <v>4</v>
+      </c>
+      <c r="AB26">
+        <v>1.67</v>
+      </c>
+      <c r="AC26">
+        <v>2.1</v>
+      </c>
+      <c r="AD26">
+        <v>2.88</v>
+      </c>
+      <c r="AE26">
+        <v>1.36</v>
+      </c>
+      <c r="AF26">
+        <v>1.73</v>
+      </c>
+      <c r="AG26">
+        <v>1.95</v>
+      </c>
+      <c r="AH26">
+        <v>5.5</v>
+      </c>
+      <c r="AI26">
         <v>1.11</v>
-      </c>
-      <c r="AA26">
-        <v>4.95</v>
-      </c>
-      <c r="AB26">
-        <v>1.61</v>
-      </c>
-      <c r="AC26">
-        <v>2.2</v>
-      </c>
-      <c r="AD26">
-        <v>2.33</v>
-      </c>
-      <c r="AE26">
-        <v>1.63</v>
-      </c>
-      <c r="AF26">
-        <v>1.82</v>
-      </c>
-      <c r="AG26">
-        <v>1.85</v>
-      </c>
-      <c r="AH26">
-        <v>3.72</v>
-      </c>
-      <c r="AI26">
-        <v>1.21</v>
       </c>
       <c r="AJ26" t="s">
         <v>121</v>
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -3886,10 +3886,10 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -4002,10 +4002,10 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -4118,10 +4118,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
         <v>86</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
         <v>88</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -199,69 +199,69 @@
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
     <t>Chrudim</t>
   </si>
   <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
+    <t>Malmö FF</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>FCSB</t>
   </si>
   <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
     <t>Panathinaikos</t>
   </si>
   <si>
@@ -292,67 +292,67 @@
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Baník Ostrava II</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Opava</t>
+    <t>Rīgas FS</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
     <t>Shkendija</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
     <t>Artsakh</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
   </si>
   <si>
     <t>Rangers</t>
@@ -1245,76 +1245,76 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M5">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="O5">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="P5">
-        <v>18.5</v>
+        <v>14.75</v>
       </c>
       <c r="Q5">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U5">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AB5">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AC5">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AD5">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AF5">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>3.94</v>
+        <v>4.7</v>
       </c>
       <c r="AI5">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ5" t="s">
         <v>121</v>
@@ -1334,10 +1334,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -1361,76 +1361,76 @@
         <v>120</v>
       </c>
       <c r="L6">
-        <v>1.14</v>
+        <v>2.11</v>
       </c>
       <c r="M6">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
-        <v>18</v>
+        <v>2.75</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q6">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="V6">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>17.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB6">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="AD6">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AE6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI6">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AJ6" t="s">
         <v>121</v>
@@ -1477,76 +1477,76 @@
         <v>120</v>
       </c>
       <c r="L7">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="M7">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
+        <v>1.79</v>
+      </c>
+      <c r="P7">
+        <v>20.5</v>
+      </c>
+      <c r="Q7">
+        <v>2.01</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>3.4</v>
+      </c>
+      <c r="T7">
         <v>2.12</v>
       </c>
-      <c r="P7">
-        <v>13.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.8</v>
-      </c>
-      <c r="R7">
-        <v>1.3</v>
-      </c>
-      <c r="S7">
-        <v>3.1</v>
-      </c>
-      <c r="T7">
-        <v>2.44</v>
-      </c>
       <c r="U7">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z7">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AA7">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC7">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD7">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AE7">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AI7">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AJ7" t="s">
         <v>121</v>
@@ -1593,76 +1593,76 @@
         <v>120</v>
       </c>
       <c r="L8">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N8">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="P8">
-        <v>20.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q8">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="T8">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V8">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AA8">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AB8">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AC8">
-        <v>2.71</v>
+        <v>2.09</v>
       </c>
       <c r="AD8">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AE8">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AF8">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH8">
-        <v>3.22</v>
+        <v>4.9</v>
       </c>
       <c r="AI8">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AJ8" t="s">
         <v>121</v>
@@ -1914,10 +1914,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>67</v>
@@ -1941,76 +1941,76 @@
         <v>120</v>
       </c>
       <c r="L11">
-        <v>3.25</v>
+        <v>1.14</v>
       </c>
       <c r="M11">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="N11">
-        <v>1.9</v>
+        <v>18</v>
       </c>
       <c r="O11">
+        <v>1.2</v>
+      </c>
+      <c r="P11">
+        <v>17</v>
+      </c>
+      <c r="Q11">
+        <v>4.8</v>
+      </c>
+      <c r="R11">
+        <v>1.22</v>
+      </c>
+      <c r="S11">
+        <v>3.9</v>
+      </c>
+      <c r="T11">
+        <v>1.98</v>
+      </c>
+      <c r="U11">
+        <v>1.71</v>
+      </c>
+      <c r="V11">
+        <v>4.2</v>
+      </c>
+      <c r="W11">
+        <v>1.2</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>17.5</v>
+      </c>
+      <c r="Z11">
+        <v>1.14</v>
+      </c>
+      <c r="AA11">
+        <v>5.25</v>
+      </c>
+      <c r="AB11">
+        <v>1.4</v>
+      </c>
+      <c r="AC11">
+        <v>2.75</v>
+      </c>
+      <c r="AD11">
         <v>2.25</v>
       </c>
-      <c r="P11">
-        <v>14.75</v>
-      </c>
-      <c r="Q11">
-        <v>1.69</v>
-      </c>
-      <c r="R11">
+      <c r="AE11">
+        <v>1.6</v>
+      </c>
+      <c r="AF11">
+        <v>2.1</v>
+      </c>
+      <c r="AG11">
+        <v>1.65</v>
+      </c>
+      <c r="AH11">
+        <v>3.3</v>
+      </c>
+      <c r="AI11">
         <v>1.29</v>
-      </c>
-      <c r="S11">
-        <v>3.28</v>
-      </c>
-      <c r="T11">
-        <v>2.45</v>
-      </c>
-      <c r="U11">
-        <v>1.5</v>
-      </c>
-      <c r="V11">
-        <v>5.8</v>
-      </c>
-      <c r="W11">
-        <v>1.13</v>
-      </c>
-      <c r="X11">
-        <v>1.04</v>
-      </c>
-      <c r="Y11">
-        <v>13</v>
-      </c>
-      <c r="Z11">
-        <v>1.15</v>
-      </c>
-      <c r="AA11">
-        <v>4.2</v>
-      </c>
-      <c r="AB11">
-        <v>1.67</v>
-      </c>
-      <c r="AC11">
-        <v>2.16</v>
-      </c>
-      <c r="AD11">
-        <v>2.53</v>
-      </c>
-      <c r="AE11">
-        <v>1.41</v>
-      </c>
-      <c r="AF11">
-        <v>1.57</v>
-      </c>
-      <c r="AG11">
-        <v>2.3</v>
-      </c>
-      <c r="AH11">
-        <v>4.6</v>
-      </c>
-      <c r="AI11">
-        <v>1.16</v>
       </c>
       <c r="AJ11" t="s">
         <v>121</v>
@@ -2030,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
@@ -2057,76 +2057,76 @@
         <v>120</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="s">
         <v>121</v>
@@ -2173,76 +2173,76 @@
         <v>120</v>
       </c>
       <c r="L13">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="M13">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="N13">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="P13">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Q13">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
         <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="Z13">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AA13">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AB13">
+        <v>1.64</v>
+      </c>
+      <c r="AC13">
+        <v>2.21</v>
+      </c>
+      <c r="AD13">
+        <v>2.47</v>
+      </c>
+      <c r="AE13">
+        <v>1.43</v>
+      </c>
+      <c r="AF13">
         <v>1.53</v>
       </c>
-      <c r="AC13">
-        <v>2.2</v>
-      </c>
-      <c r="AD13">
-        <v>2.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.5</v>
-      </c>
-      <c r="AF13">
-        <v>1.5</v>
-      </c>
       <c r="AG13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH13">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI13">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ13" t="s">
         <v>121</v>
@@ -2262,10 +2262,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
@@ -2289,76 +2289,76 @@
         <v>120</v>
       </c>
       <c r="L14">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -2405,76 +2405,76 @@
         <v>120</v>
       </c>
       <c r="L15">
-        <v>2.19</v>
+        <v>1.71</v>
       </c>
       <c r="M15">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O15">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="P15">
-        <v>15.75</v>
+        <v>18.5</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="U15">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z15">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA15">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AB15">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AD15">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AE15">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH15">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AI15">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="s">
         <v>121</v>
@@ -2842,10 +2842,10 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -2869,76 +2869,76 @@
         <v>120</v>
       </c>
       <c r="L19">
+        <v>1.35</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19">
+        <v>8</v>
+      </c>
+      <c r="O19">
+        <v>1.27</v>
+      </c>
+      <c r="P19">
+        <v>15.5</v>
+      </c>
+      <c r="Q19">
+        <v>3.9</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.6</v>
+      </c>
+      <c r="T19">
+        <v>2.15</v>
+      </c>
+      <c r="U19">
+        <v>1.62</v>
+      </c>
+      <c r="V19">
+        <v>4.6</v>
+      </c>
+      <c r="W19">
+        <v>1.16</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>19.5</v>
+      </c>
+      <c r="Z19">
         <v>1.1</v>
       </c>
-      <c r="M19">
-        <v>8</v>
-      </c>
-      <c r="N19">
-        <v>11</v>
-      </c>
-      <c r="O19">
-        <v>1.18</v>
-      </c>
-      <c r="P19">
-        <v>29</v>
-      </c>
-      <c r="Q19">
-        <v>4.6</v>
-      </c>
-      <c r="R19">
-        <v>1.13</v>
-      </c>
-      <c r="S19">
-        <v>5.25</v>
-      </c>
-      <c r="T19">
+      <c r="AA19">
+        <v>5.15</v>
+      </c>
+      <c r="AB19">
         <v>1.6</v>
       </c>
-      <c r="U19">
-        <v>2.15</v>
-      </c>
-      <c r="V19">
-        <v>2.87</v>
-      </c>
-      <c r="W19">
-        <v>1.36</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>1.01</v>
-      </c>
-      <c r="AA19">
-        <v>10</v>
-      </c>
-      <c r="AB19">
-        <v>1.2</v>
-      </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE19">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH19">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="AI19">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="s">
         <v>121</v>
@@ -2958,10 +2958,10 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
         <v>76</v>
@@ -2985,76 +2985,76 @@
         <v>120</v>
       </c>
       <c r="L20">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q20">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S20">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T20">
+        <v>1.6</v>
+      </c>
+      <c r="U20">
         <v>2.15</v>
       </c>
-      <c r="U20">
-        <v>1.62</v>
-      </c>
       <c r="V20">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
         <v>1.01</v>
       </c>
-      <c r="Y20">
-        <v>19.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.1</v>
-      </c>
       <c r="AA20">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC20">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD20">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE20">
+        <v>2.45</v>
+      </c>
+      <c r="AF20">
         <v>1.73</v>
       </c>
-      <c r="AF20">
-        <v>1.9</v>
-      </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH20">
-        <v>3.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI20">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AJ20" t="s">
         <v>121</v>
@@ -3306,10 +3306,10 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
@@ -3333,76 +3333,76 @@
         <v>120</v>
       </c>
       <c r="L23">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="M23">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="N23">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P23">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S23">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U23">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z23">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AA23">
-        <v>4.95</v>
+        <v>6.25</v>
       </c>
       <c r="AB23">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC23">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD23">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AE23">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AF23">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
         <v>1.85</v>
       </c>
       <c r="AH23">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="AI23">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="s">
         <v>121</v>
@@ -3538,10 +3538,10 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
         <v>81</v>
@@ -3565,76 +3565,76 @@
         <v>120</v>
       </c>
       <c r="L25">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="M25">
-        <v>7.02</v>
+        <v>4.5</v>
       </c>
       <c r="N25">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="O25">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P25">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q25">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="R25">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AA25">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="AB25">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AE25">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF25">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH25">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AI25">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AJ25" t="s">
         <v>121</v>
@@ -3729,10 +3729,10 @@
         <v>4</v>
       </c>
       <c r="AB26">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD26">
         <v>2.88</v>
@@ -3967,10 +3967,10 @@
         <v>2.2</v>
       </c>
       <c r="AD28">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AE28">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AF28">
         <v>1.68</v>
@@ -4077,10 +4077,10 @@
         <v>3.55</v>
       </c>
       <c r="AB29">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AD29">
         <v>2.97</v>
@@ -4264,10 +4264,10 @@
         <v>2.5</v>
       </c>
       <c r="M31">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="O31">
         <v>1.95</v>
@@ -4279,22 +4279,22 @@
         <v>1.91</v>
       </c>
       <c r="R31">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
         <v>2.5</v>
       </c>
       <c r="U31">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V31">
         <v>5.75</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -4303,34 +4303,34 @@
         <v>10.9</v>
       </c>
       <c r="Z31">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AA31">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB31">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC31">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD31">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AE31">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH31">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AI31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="s">
         <v>121</v>
@@ -4377,13 +4377,13 @@
         <v>120</v>
       </c>
       <c r="L32">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="M32">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N32">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="O32">
         <v>1.62</v>
@@ -4395,22 +4395,22 @@
         <v>2.5</v>
       </c>
       <c r="R32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S32">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T32">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="U32">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V32">
         <v>6</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
         <v>1.02</v>
@@ -4422,25 +4422,25 @@
         <v>1.24</v>
       </c>
       <c r="AA32">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AB32">
         <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE32">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF32">
         <v>1.76</v>
       </c>
       <c r="AG32">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH32">
         <v>5.5</v>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="P10" t="n">
-        <v>20.5</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH10" t="n">
         <v>4.5</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.14</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>7.4</v>
+        <v>3.51</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>13.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="O13" t="n">
         <v>1.61</v>
@@ -2144,55 +2144,55 @@
         <v>2.33</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>13.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AI13" t="n">
         <v>1.22</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="P17" t="n">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.57</v>
       </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>4.85</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.24</v>
       </c>
-      <c r="P21" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
         <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
         <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.44</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.58</v>
-      </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.21</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF25" t="n">
         <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O26" t="n">
         <v>1.25</v>
@@ -3860,55 +3860,55 @@
         <v>3.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S26" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
         <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AA26" t="n">
         <v>6.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
         <v>3.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AI26" t="n">
         <v>1.36</v>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.95</v>
@@ -4520,58 +4520,58 @@
         <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="O32" t="n">
         <v>1.62</v>
@@ -4652,16 +4652,16 @@
         <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
         <v>6</v>
@@ -4670,40 +4670,40 @@
         <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.449999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AA32" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.3</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH32" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>20.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.74</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,73 +1994,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>3.29</v>
       </c>
       <c r="M12" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>13.25</v>
+        <v>14.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI12" t="n">
         <v>1.15</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.29</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="P14" t="n">
-        <v>14.75</v>
+        <v>16.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
         <v>2.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,58 +2390,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="P15" t="n">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>12.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
         <v>2.5</v>
@@ -2450,16 +2450,16 @@
         <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.35</v>
+        <v>4.85</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P16" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P16" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="V16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.18</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA16" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="N17" t="n">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
@@ -2693,34 +2693,34 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE17" t="n">
         <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AI17" t="n">
         <v>1.17</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P19" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="AA19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC19" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.32</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG21" t="n">
         <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.24</v>
       </c>
-      <c r="P22" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG22" t="n">
         <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF24" t="n">
         <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.44</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.58</v>
-      </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.21</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.3</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.18</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA10" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="P12" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,58 +2390,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P15" t="n">
-        <v>15.75</v>
+        <v>16.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>12.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
         <v>2.5</v>
@@ -2450,16 +2450,16 @@
         <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.85</v>
+        <v>4.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,73 +2522,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>3.29</v>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>13.25</v>
+        <v>14.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI16" t="n">
         <v>1.15</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="P17" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
@@ -2693,34 +2693,34 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AI17" t="n">
         <v>1.17</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.15</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA19" t="n">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.32</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.1</v>
       </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="AA20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.89</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="P26" t="n">
-        <v>20.5</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.92</v>
+        <v>2.55</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="M5" t="n">
         <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>3.54</v>
       </c>
       <c r="O5" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,37 +1994,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>13.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
@@ -2036,34 +2036,34 @@
         <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
         <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.41</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>2.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.29</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="P16" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
         <v>2.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
         <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,58 +2654,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N17" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>15.75</v>
+        <v>16.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>12.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD17" t="n">
         <v>2.5</v>
@@ -2714,16 +2714,16 @@
         <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.85</v>
+        <v>4.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P19" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="AA19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC19" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.32</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,40 +806,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -848,34 +848,34 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         <v>1.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="N5" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.61</v>
@@ -1088,58 +1088,58 @@
         <v>2.33</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.14</v>
+        <v>2.18</v>
       </c>
       <c r="M8" t="n">
-        <v>7.4</v>
+        <v>3.67</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="P8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
         <v>17</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
         <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="P14" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.93</v>
+        <v>2.49</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>2.25</v>
@@ -2408,58 +2408,58 @@
         <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="Z15" t="n">
         <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="M17" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="O17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="P17" t="n">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
         <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.35</v>
+        <v>5.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="M18" t="n">
-        <v>3.54</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>13.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.53</v>
       </c>
-      <c r="V18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
         <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.15</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA19" t="n">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>4.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.32</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.1</v>
       </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="AA20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3236,10 +3236,10 @@
         <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
         <v>1.96</v>
@@ -3362,10 +3362,10 @@
         <v>2.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
         <v>3.48</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="P23" t="n">
-        <v>20.5</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>2.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.36</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>20.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>7.25</v>
+        <v>3.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.1</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AG25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD25" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH25" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4028,10 +4028,10 @@
         <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
         <v>1.49</v>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="O31" t="n">
         <v>1.95</v>
@@ -4520,58 +4520,58 @@
         <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
         <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC31" t="n">
         <v>1.86</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AE31" t="n">
         <v>1.33</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N32" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="O32" t="n">
         <v>1.62</v>
@@ -4652,58 +4652,58 @@
         <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL32"/>
+  <dimension ref="A1:AL34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,40 +674,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -716,34 +716,34 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,40 +806,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -848,34 +848,34 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>1.14</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>2.16</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>2.49</v>
       </c>
       <c r="M13" t="n">
-        <v>7.4</v>
+        <v>3.62</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>2.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.29</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="P14" t="n">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
-        <v>14.75</v>
+        <v>13.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="U15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.44</v>
       </c>
-      <c r="V15" t="n">
-        <v>6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.81</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.16</v>
+        <v>3.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>15.75</v>
+        <v>14.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
         <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
         <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="P18" t="n">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>5.25</v>
+        <v>6.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
         <v>11</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P25" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Z25" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>1.17</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>20.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>3.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
-        <v>7.25</v>
+        <v>3.9</v>
       </c>
       <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.08</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AA26" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.2</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD26" t="n">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.4</v>
+        <v>2.62</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="N29" t="n">
-        <v>2.12</v>
+        <v>6.17</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4329,27 +4329,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4373,73 +4373,73 @@
         <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45868.85416666666</v>
+        <v>45868.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.91</v>
+        <v>1.81</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="V31" t="n">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45868.875</v>
+        <v>45868.85416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4593,129 +4593,393 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>45868.875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>45868.88194444445</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="L34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.62</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P34" t="n">
         <v>11.75</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q34" t="n">
         <v>2.5</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.33</v>
       </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AF34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="n">
         <v>45868.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -657,20 +657,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '11', '25']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -789,20 +789,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -924,17 +924,17 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '75', '83']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1034,121 +1034,121 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '6', '80']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1166,112 +1166,112 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '45+2', '61']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1308,29 +1308,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66', '72']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+3']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1440,29 +1440,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '45', '83']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1581,20 +1581,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '17']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '45', '86']</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1694,26 +1694,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1726,84 +1726,84 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>7.4</v>
+        <v>3.57</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>2.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>13.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '82']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1836,29 +1836,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '89']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1968,16 +1968,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1990,84 +1990,84 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="P12" t="n">
-        <v>18.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2122,32 +2122,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="P13" t="n">
-        <v>16.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
         <v>2.27</v>
@@ -2156,46 +2156,46 @@
         <v>1.59</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,106 +2232,106 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>3.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>15.75</v>
+        <v>14.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
         <v>2.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '78']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2364,111 +2364,111 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.05</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AH15" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '69']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '32']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,121 +2486,121 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '58', '69']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '82']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2650,80 +2650,80 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,116 +2750,116 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>18</v>
       </c>
       <c r="O18" t="n">
-        <v>2.16</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2901,20 +2901,20 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3033,20 +3033,20 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.24</v>
       </c>
-      <c r="P21" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
         <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,111 +3288,111 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
         <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '87']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF23" t="n">
         <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="n">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="P24" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.33</v>
+        <v>3.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AF24" t="n">
         <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.72</v>
+        <v>6.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,121 +3674,121 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.17</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>20.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.55</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>7.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '76']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.17</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="P26" t="n">
-        <v>20.5</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.92</v>
+        <v>2.55</v>
       </c>
       <c r="R26" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>3.9</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>7.03</v>
+        <v>4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>6.17</v>
+        <v>2.12</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="N30" t="n">
-        <v>2.12</v>
+        <v>6.17</v>
       </c>
       <c r="O30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
         <v>2.3</v>
@@ -4520,58 +4520,58 @@
         <v>1.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.15</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.22</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -1034,121 +1034,121 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>['3', '6', '80']</t>
+          <t>['48', '58', '69']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['13', '82']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '17']</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>['19', '45+2', '61']</t>
+          <t>['30', '45', '86']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1308,26 +1308,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>['66', '72']</t>
+          <t>['68', '89']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>['28', '90+3']</t>
+          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,25 +1572,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1598,85 +1598,85 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>['8', '17']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>['30', '45', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1694,35 +1694,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,85 +1730,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['54', '82']</t>
+          <t>['66', '72']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+3']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1836,25 +1836,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['68', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1968,16 +1968,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1997,77 +1997,77 @@
         <v>2.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="P12" t="n">
-        <v>15.75</v>
+        <v>20.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['54', '82']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2100,25 +2100,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,85 +2126,85 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.05</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.81</v>
-      </c>
       <c r="AH13" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '69']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '32']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2232,22 +2232,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2258,80 +2258,80 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
         <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="P14" t="n">
-        <v>14.75</v>
+        <v>13.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.44</v>
       </c>
-      <c r="V14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>['44', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2390,85 +2390,85 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2.1</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>['61', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>['5', '32']</t>
+          <t>['19', '45+2', '61']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,35 +2486,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2522,85 +2522,85 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>['48', '58', '69']</t>
+          <t>['44', '78']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>['13', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2618,26 +2618,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2654,80 +2654,80 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2750,32 +2750,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2786,85 +2786,85 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>7.4</v>
+        <v>3.62</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['3', '6', '80']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,80 +2918,80 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P19" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="AA19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC19" t="n">
-        <v>4.66</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>3.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,80 +3050,80 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5.15</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>4.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.32</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3156,111 +3156,111 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>19.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.1</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG21" t="n">
         <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.75</v>
+        <v>3.64</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '87']</t>
         </is>
       </c>
       <c r="AL21" s="3" t="n">
@@ -3288,25 +3288,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
         <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.24</v>
       </c>
-      <c r="P22" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG22" t="n">
         <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.64</v>
+        <v>6.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['107', '117', '19']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>['33', '87']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
@@ -3420,19 +3420,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3442,89 +3442,89 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.44</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.58</v>
-      </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.11</v>
       </c>
-      <c r="AA23" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AL23" s="3" t="n">
@@ -3552,111 +3552,111 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.1</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AF24" t="n">
         <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.4</v>
+        <v>3.72</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '12', '52', '74']</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '22', '70']</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3674,121 +3674,121 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="P25" t="n">
-        <v>20.5</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>3.9</v>
+        <v>7.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>26</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AA25" t="n">
-        <v>7.03</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.62</v>
+        <v>6.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>['16', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3806,121 +3806,121 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.17</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>20.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.55</v>
+        <v>3.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>4</v>
+        <v>7.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '76']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3960,17 +3960,17 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4089,20 +4089,20 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AL28" s="3" t="n">
@@ -4202,121 +4202,121 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="N29" t="n">
-        <v>2.12</v>
+        <v>6.17</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.97</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '39', '84']</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AL29" s="3" t="n">
@@ -4334,121 +4334,121 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>6.17</v>
+        <v>2.12</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '31', '87']</t>
         </is>
       </c>
       <c r="AL30" s="3" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL34"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -638,32 +633,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -674,40 +669,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -716,46 +711,43 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.39</v>
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['4', '11', '25']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45868.5</v>
       </c>
     </row>
@@ -770,32 +762,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -806,88 +798,85 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.3</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['4', '11', '25']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45868.5</v>
       </c>
     </row>
@@ -994,11 +983,15 @@
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['1', '75', '83']</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1009,17 +1002,10 @@
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['1', '75', '83']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45868.52083333334</v>
       </c>
     </row>
@@ -1034,26 +1020,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -1062,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1070,88 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['61', '69']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['5', '32']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>['48', '58', '69']</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>['13', '82']</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1176,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1258,11 +1241,15 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1273,17 +1260,10 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>['8', '17']</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>['30', '45', '86']</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1308,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -1390,11 +1370,15 @@
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['8', '17']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['30', '45', '86']</t>
+        </is>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1405,17 +1389,10 @@
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['68', '89']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1440,26 +1417,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -1522,11 +1499,15 @@
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['68', '89']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
+        </is>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1537,17 +1518,10 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>['34', '45', '83']</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1562,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,114 +1546,111 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['48', '58', '69']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['13', '82']</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1694,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,88 +1701,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>['66', '72']</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>['28', '90+3']</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1836,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1918,11 +1886,15 @@
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['34', '45', '83']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1933,17 +1905,10 @@
       <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -1958,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1994,88 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.14</v>
       </c>
       <c r="M12" t="n">
-        <v>3.57</v>
+        <v>7.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>20.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.01</v>
+        <v>9.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y12" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AH12" t="n">
-        <v>4.09</v>
+        <v>4.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>['54', '82']</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2090,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2118,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,88 +2088,85 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['66', '72']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['28', '90+3']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>['61', '69']</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>['5', '32']</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2232,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2258,88 +2217,85 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
         <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.12</v>
+        <v>3.92</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>5.15</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.12</v>
+        <v>1.87</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['44', '78']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.81</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.7</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2399,13 +2355,13 @@
         <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.61</v>
+        <v>2.43</v>
       </c>
       <c r="P15" t="n">
-        <v>18.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.33</v>
+        <v>3.96</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -2420,58 +2376,55 @@
         <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
         <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.14</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['19', '45+2', '61']</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>2.55</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>['19', '45+2', '61']</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2496,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2511,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2522,88 +2475,85 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.32</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2.25</v>
       </c>
-      <c r="P16" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AA16" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['54', '82']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>['44', '78']</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2628,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2654,88 +2604,85 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>15.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>2.81</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK17" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2795,13 +2742,13 @@
         <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>16.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -2816,58 +2763,55 @@
         <v>1.59</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>4.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>2.52</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['3', '6', '80']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.52</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>['3', '6', '80']</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45868.54166666666</v>
       </c>
     </row>
@@ -2882,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,88 +2862,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="T19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.15</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>4.6</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+      <c r="AK19" s="3" t="n">
         <v>45868.58333333334</v>
       </c>
     </row>
@@ -3014,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,88 +2991,85 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.1</v>
       </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.6</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.66</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>3.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45868.58333333334</v>
       </c>
     </row>
@@ -3191,13 +3129,13 @@
         <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>19.75</v>
+        <v>2.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.21</v>
@@ -3212,58 +3150,55 @@
         <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['33', '87']</t>
+        </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>['33', '87']</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45868.60416666666</v>
       </c>
     </row>
@@ -3323,13 +3258,13 @@
         <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>2.55</v>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.43</v>
@@ -3344,58 +3279,55 @@
         <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>7.75</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>2.97</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>3.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['107', '117', '19']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>['107', '117', '19']</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45868.60416666666</v>
       </c>
     </row>
@@ -3410,32 +3342,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3446,88 +3378,85 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>1.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>7.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="S23" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>7.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['16', '76']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AH23" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK23" s="3" t="n">
         <v>45868.625</v>
       </c>
     </row>
@@ -3552,114 +3481,111 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>1.64</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>['1', '12', '52', '74']</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>['7', '22', '70']</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45868.625</v>
       </c>
     </row>
@@ -3719,13 +3645,13 @@
         <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
@@ -3740,58 +3666,55 @@
         <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.1</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45868.625</v>
       </c>
     </row>
@@ -3806,35 +3729,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3842,88 +3765,85 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N26" t="n">
         <v>6.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="P26" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.92</v>
+        <v>6.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>4.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>1.61</v>
       </c>
       <c r="Z26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['1', '12', '52', '74']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['7', '22', '70']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.08</v>
       </c>
-      <c r="AA26" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>['16', '76']</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45868.625</v>
       </c>
     </row>
@@ -3983,13 +3903,13 @@
         <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>14.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
@@ -4004,58 +3924,55 @@
         <v>1.63</v>
       </c>
       <c r="V27" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>22</v>
+        <v>1.73</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>2</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH27" t="n">
-        <v>3.48</v>
+        <v>1.23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45868.64583333334</v>
       </c>
     </row>
@@ -4115,13 +4032,13 @@
         <v>6.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="P28" t="n">
-        <v>16</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
@@ -4136,58 +4053,55 @@
         <v>1.68</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>5.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>17</v>
+        <v>1.61</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.75</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.05</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK28" s="3" t="n">
         <v>45868.65625</v>
       </c>
     </row>
@@ -4202,124 +4116,121 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>6.17</v>
+        <v>2.12</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>1.17</v>
+        <v>3.55</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['28', '31', '87']</t>
+        </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>1.27</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>['9', '39', '84']</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AL29" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK29" s="3" t="n">
         <v>45868.66666666666</v>
       </c>
     </row>
@@ -4334,124 +4245,121 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['9', '39', '84']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AI30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>['28', '31', '87']</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3" t="n">
         <v>45868.66666666666</v>
       </c>
     </row>
@@ -4485,20 +4393,20 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4511,13 +4419,13 @@
         <v>1.93</v>
       </c>
       <c r="O31" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
         <v>1.33</v>
@@ -4532,58 +4440,55 @@
         <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.16</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['22', '51']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['11', '38']</t>
+        </is>
       </c>
       <c r="AG31" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.3</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK31" s="3" t="n">
         <v>45868.85416666666</v>
       </c>
     </row>
@@ -4617,105 +4522,102 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N32" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="O32" t="n">
+      <c r="T32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['17', '24', '26', '82']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.95</v>
       </c>
-      <c r="P32" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="AJ32" t="n">
         <v>1.91</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AK32" s="3" t="n">
         <v>45868.875</v>
       </c>
     </row>
@@ -4749,39 +4651,39 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
         <v>1.55</v>
@@ -4796,58 +4698,55 @@
         <v>1.22</v>
       </c>
       <c r="V33" t="n">
-        <v>10.5</v>
+        <v>1.08</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X33" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.2</v>
+        <v>2.85</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.35</v>
+        <v>5.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.6</v>
+        <v>1.13</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['45+2', '75']</t>
+        </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK33" s="3" t="n">
         <v>45868.88194444445</v>
       </c>
     </row>
@@ -4881,105 +4780,102 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.7</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="AD34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['20', '58', '72', '89']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.62</v>
       </c>
-      <c r="P34" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="AJ34" t="n">
         <v>2.5</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL34" s="3" t="n">
+      <c r="AK34" s="3" t="n">
         <v>45868.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-30.xlsx
+++ b/jogos_2025-07-30.xlsx
@@ -633,32 +633,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -669,65 +669,65 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['4', '11', '25']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45868.5</v>
@@ -762,32 +762,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['4', '11', '25']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45868.5</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['61', '69']</t>
+          <t>['54', '82']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['5', '32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1278,35 +1278,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['8', '17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['30', '45', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1407,35 +1407,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['68', '89']</t>
+          <t>['44', '78']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1536,119 +1536,119 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['48', '58', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['13', '82']</t>
+          <t>['19', '45+2', '61']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1665,119 +1665,119 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['48', '58', '69']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '82']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1822,7 +1822,7 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['34', '45', '83']</t>
+          <t>['3', '6', '80']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45868.54166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['66', '72']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+3']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45868.54166666666</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['66', '72']</t>
+          <t>['34', '45', '83']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['28', '90+3']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.32</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
         <v>2.2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['44', '78']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45868.54166666666</v>
@@ -2310,35 +2310,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>3.99</v>
+        <v>7.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
-        <v>2.43</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.96</v>
+        <v>9.25</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
         <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
         <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['19', '45+2', '61']</t>
-        </is>
-      </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.92</v>
+        <v>4.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.33</v>
+        <v>4.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45868.54166666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.38</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['61', '69']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['5', '32']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['54', '82']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45868.54166666666</v>
@@ -2568,35 +2568,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '17']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '45', '86']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45868.54166666666</v>
@@ -2697,119 +2697,119 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['3', '6', '80']</t>
+          <t>['68', '89']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['16', '24', '61', '72', '77', '90+1', '90+4']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45868.54166666666</v>
@@ -3342,32 +3342,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.17</v>
+        <v>2.01</v>
       </c>
       <c r="M23" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.05</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>7.03</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['16', '76']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.92</v>
+        <v>2.55</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45868.625</v>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45868.625</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>6.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.32</v>
+        <v>2.33</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
         <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '12', '52', '74']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['7', '22', '70']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45868.625</v>
@@ -3729,35 +3729,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="M26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S26" t="n">
         <v>4.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="T26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.78</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.58</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>4.95</v>
+        <v>7.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['1', '12', '52', '74']</t>
+          <t>['16', '76']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['7', '22', '70']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45868.625</v>
@@ -4116,119 +4116,119 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>3</v>
-      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['9', '39', '84']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['28', '31', '87']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AI29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45868.66666666666</v>
@@ -4245,119 +4245,119 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>6.17</v>
+        <v>2.12</v>
       </c>
       <c r="O30" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="X30" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['9', '39', '84']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['28', '31', '87']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45868.66666666666</v>
